--- a/www/download/IND.surplus_value.empe_hs.r.pc.WIOD13.xlsx
+++ b/www/download/IND.surplus_value.empe_hs.r.pc.WIOD13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>0.104015780973202</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>0.0664645432035125</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>0.0931973074335934</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>0.0904893400612632</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>0.0124448614249786</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>0.0915599177083997</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>0.120564611766825</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>0.088975272507847</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>0.0277542998423554</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-12.27</t>
+          <t>-0.122645340667946</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-16.98</t>
+          <t>-0.169705375587354</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-14.24</t>
+          <t>-0.142363196945882</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-14.99</t>
+          <t>-0.149743381724477</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-0.0625760502570983</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.0205630692132253</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-36.7</t>
+          <t>-0.36697142435328</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-34.28</t>
+          <t>-0.342786052328007</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-0.206906613298569</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-20.95</t>
+          <t>-0.209543224006525</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-20.61</t>
+          <t>-0.216008556679436</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-14.99</t>
+          <t>-0.149868284622965</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-15.06</t>
+          <t>-0.150588501749006</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.75</t>
+          <t>-0.157394699900883</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-19.21</t>
+          <t>-0.191960899746963</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-24.69</t>
+          <t>-0.246880031357208</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>-0.256673288442381</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-27.55</t>
+          <t>-0.275511282792211</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-27.76</t>
+          <t>-0.277429699185534</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-26.01</t>
+          <t>-0.260057715624549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-20.02</t>
+          <t>-0.200170697315601</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-47.33</t>
+          <t>-0.473267816049411</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-47.98</t>
+          <t>-0.479802493529803</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-45.1</t>
+          <t>-0.450956739306515</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-44.43</t>
+          <t>-0.444298422443381</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-49.14</t>
+          <t>-0.499614150338939</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-49.75</t>
+          <t>-0.497413172267108</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-52.33</t>
+          <t>-0.52320178911202</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-55.52</t>
+          <t>-0.555105132917792</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-60.98</t>
+          <t>-0.609739203476388</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.27</t>
+          <t>-0.652652136267561</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-64.75</t>
+          <t>-0.647455497569256</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-64.27</t>
+          <t>-0.642656028864535</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-62.1</t>
+          <t>-0.620966450748709</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-56.52</t>
+          <t>-0.565228865227056</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-58.53</t>
+          <t>-0.585232980862737</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>134.26</t>
+          <t>1.34273067086233</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>171.29</t>
+          <t>1.71303358854145</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>209.02</t>
+          <t>2.09026326458875</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>116.87</t>
+          <t>1.16864920122973</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>132.63</t>
+          <t>1.27828329337813</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>1.26711480242452</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>118.38</t>
+          <t>1.1839021107581</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>117.43</t>
+          <t>1.17452226928308</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>1.81015021924516</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>129.9</t>
+          <t>1.29895581294224</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>135.26</t>
+          <t>1.35264983076965</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>144.54</t>
+          <t>1.44556732221005</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>144.72</t>
+          <t>1.44734298073836</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>120.65</t>
+          <t>1.20640064430053</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>104.26</t>
+          <t>1.04269169123318</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-28.41</t>
+          <t>-0.284006561992249</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-26.82</t>
+          <t>-0.268141233354191</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-20.81</t>
+          <t>-0.20806227088467</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-21.01</t>
+          <t>-0.210082165049577</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.64</t>
+          <t>-0.154805884954127</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-0.0532515908262146</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.00802849039896469</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>0.0432271154952524</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>0.104673115265164</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>0.126569011249237</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>0.102182844786283</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>0.149921466801928</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>0.203103438135202</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>0.210352465199749</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>0.259236343578809</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>0.422394132347846</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>0.425567422864574</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>0.480197970860446</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>0.39117343938986</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>31.79</t>
+          <t>0.291691968574261</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>0.226112982166399</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>0.151749780394588</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>0.138811641555345</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>0.0818473124152321</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>0.0485796114437587</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.0102436169769761</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-0.0453210228898412</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.0101694652086333</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>0.0424998216784966</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>0.152522546846726</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-50.52</t>
+          <t>-0.505213126133137</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-47.93</t>
+          <t>-0.479282896872297</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-50.04</t>
+          <t>-0.500412363181639</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-51.15</t>
+          <t>-0.511501803548544</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-51.67</t>
+          <t>-0.526274555126516</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-50.53</t>
+          <t>-0.505269869776754</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-46.47</t>
+          <t>-0.464631047110428</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-44.36</t>
+          <t>-0.443583152809506</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-42.04</t>
+          <t>-0.42040847456927</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-36.8</t>
+          <t>-0.368018271520238</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-33.22</t>
+          <t>-0.332218799374668</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>-32.69</t>
+          <t>-0.32692258183145</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-26.35</t>
+          <t>-0.263480755958882</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-26.75</t>
+          <t>-0.26748249090098</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-24.5</t>
+          <t>-0.24498100941157</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>0.314880975756053</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>0.289474802170022</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>0.471816514580483</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.43</t>
+          <t>0.384281673770632</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>26.99</t>
+          <t>0.247021010466021</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>0.297179398557758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>0.224951428731801</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>0.208508449438505</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>0.0960695945635355</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8.41</t>
+          <t>0.0840927889528962</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>0.104189979386306</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>0.127523764830177</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>27.21</t>
+          <t>0.272229515988968</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>0.113596063371232</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>0.355662415923796</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>164.64</t>
+          <t>1.64720228198353</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>0.843813326582864</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>99.38</t>
+          <t>0.99383873662643</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>98.39</t>
+          <t>0.983854152417042</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>99.71</t>
+          <t>0.977179682645578</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>109.74</t>
+          <t>1.09748807792617</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>0.87672224827934</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>80.62</t>
+          <t>0.806492018388578</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>81.88</t>
+          <t>0.818882028086922</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>54.33</t>
+          <t>0.543283588585614</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>0.49955802960866</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>55.24</t>
+          <t>0.552474735579245</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>52.11</t>
+          <t>0.521270117156951</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>61.42</t>
+          <t>0.614250668190158</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>0.849137001520768</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-38.73</t>
+          <t>-0.387204848589558</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-33.25</t>
+          <t>-0.332660707877182</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-24.6</t>
+          <t>-0.246083625525126</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-25.7</t>
+          <t>-0.257081410476976</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-26.32</t>
+          <t>-0.273415287611162</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-30.06</t>
+          <t>-0.300417936822566</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-28.07</t>
+          <t>-0.28106742482083</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-29.1</t>
+          <t>-0.290622049545002</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-37.76</t>
+          <t>-0.377343891255406</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-37.27</t>
+          <t>-0.372947948400247</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-35.33</t>
+          <t>-0.353446356482576</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-37.06</t>
+          <t>-0.370539746984675</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-38.33</t>
+          <t>-0.382927148446468</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-34.13</t>
+          <t>-0.341307574164643</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-31.16</t>
+          <t>-0.311610831730092</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-29.2</t>
+          <t>-0.291944678346969</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-27.03</t>
+          <t>-0.270214479052244</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-0.0295553343253024</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-0.120013484602415</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.86</t>
+          <t>-0.14137149004825</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-0.0934120695494324</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-0.130124251652871</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-0.155851583139991</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-26.5</t>
+          <t>-0.26497532368705</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-27.01</t>
+          <t>-0.270076391351688</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-25.52</t>
+          <t>-0.255224335452692</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-25.61</t>
+          <t>-0.256053851837141</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-25.8</t>
+          <t>-0.257934324794992</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-19.73</t>
+          <t>-0.197304356669184</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-11.53</t>
+          <t>-0.115259999604788</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.0269996853979038</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>0.0430219586449672</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>0.248101409510548</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>0.163393761081219</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>0.0964138429453425</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>0.199715133044225</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>0.135201989996058</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>0.0852067398896657</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>0.0617994730516467</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-0.0351791355711308</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-0.0333336760481748</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.0365839837802818</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.0208789785640822</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.00894244824424861</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>0.12898738623987</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>181.74</t>
+          <t>1.8178174588626</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>162.34</t>
+          <t>1.62378647153876</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>152.44</t>
+          <t>1.52461460764054</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>131.51</t>
+          <t>1.31517812808268</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>129.41</t>
+          <t>1.25870758220275</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>97.08</t>
+          <t>0.971128612458655</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>104.24</t>
+          <t>1.04303864863199</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>66.95</t>
+          <t>0.669736414452915</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>0.488937277643452</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.84</t>
+          <t>0.408991035620016</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>55.62</t>
+          <t>0.556287252274289</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>0.610529982453126</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>63.82</t>
+          <t>0.638359074276649</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>52.41</t>
+          <t>0.524201620459688</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>62.21</t>
+          <t>0.622192579718947</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>0.109439599442192</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>0.0874877130187315</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>30.71</t>
+          <t>0.307798678746406</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>0.211164011523543</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>17.79</t>
+          <t>0.16365969180111</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>0.293516331645645</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>27.09</t>
+          <t>0.271865908087177</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>25.31</t>
+          <t>0.253722095583576</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>0.170316885913151</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>0.0646544738612245</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.0366249699172578</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.0016636029093241</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.00813992000754693</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0154622286940209</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>0.0785609415567143</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-20.87</t>
+          <t>-0.208660176219131</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-21.02</t>
+          <t>-0.210160997738373</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-0.0433381360857844</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-13.2</t>
+          <t>-0.131993331982912</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-0.183165491242185</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-17.31</t>
+          <t>-0.172944801734752</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-21.35</t>
+          <t>-0.213326312839444</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-23.86</t>
+          <t>-0.238461061097892</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-24.12</t>
+          <t>-0.241109651449648</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-29.5</t>
+          <t>-0.294998696083098</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-28.61</t>
+          <t>-0.286023874162032</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-25.56</t>
+          <t>-0.255552600434238</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-24.3</t>
+          <t>-0.242863102519956</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-21.14</t>
+          <t>-0.21137733772219</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-14.6</t>
+          <t>-0.145949460681819</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>0.0998192462865755</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>0.0687790253920271</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>0.16242977712851</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>0.0674644708279455</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.01126762902089</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.0121075055104375</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-0.0475169345585197</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-0.0693041499595339</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-13.52</t>
+          <t>-0.135137579453755</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-18.04</t>
+          <t>-0.180394842557198</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-17.28</t>
+          <t>-0.172785354285181</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-16.97</t>
+          <t>-0.169678110303153</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>-0.13520175118397</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-0.0333509963297783</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>0.080960722136771</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>54.56</t>
+          <t>0.545656394923493</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>0.483480393349375</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>49.41</t>
+          <t>0.49406224884981</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>0.554241192518931</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>0.459852013579773</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>40.31</t>
+          <t>0.403104816960659</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>0.429956691638624</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>0.268864302256491</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>0.301757648993717</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>0.294989281729475</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>34.12</t>
+          <t>0.341021008958166</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>0.393271197330409</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>0.329608889053254</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>0.311693238738243</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>28.83</t>
+          <t>0.288438208188191</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>46.11</t>
+          <t>0.461377579465617</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>50.55</t>
+          <t>0.505738996391414</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>0.595178269034987</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.56</t>
+          <t>0.615630871015278</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>0.51353955453072</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>54.61</t>
+          <t>0.546273661813775</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>0.600642173074804</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>0.468077006666234</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>54.58</t>
+          <t>0.546032279293171</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>60.61</t>
+          <t>0.606050425578851</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>62.33</t>
+          <t>0.623381911139004</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>0.726423239195997</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>66.05</t>
+          <t>0.660779725885431</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>0.837156918261036</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>1.03201348783328</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-0.0427825742854558</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>0.168891710377191</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>0.470954623636021</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>79.95</t>
+          <t>0.799475198183805</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>120.72</t>
+          <t>1.19547648556022</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>0.470561593540435</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>0.422160967093677</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>0.420795087451028</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>0.220518834231567</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>0.346576327719058</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-0.0450039806470561</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-0.0786579493105993</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>-20.65</t>
+          <t>-0.20650086773646</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-17.36</t>
+          <t>-0.173585592801257</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>-20.39</t>
+          <t>-0.203919801281824</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-55.85</t>
+          <t>-0.558463042520968</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-51.27</t>
+          <t>-0.512730863476844</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-53.08</t>
+          <t>-0.530818645500468</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-53.72</t>
+          <t>-0.537167337726057</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-52.76</t>
+          <t>-0.531607164633376</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-52.76</t>
+          <t>-0.527563707871258</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-52.48</t>
+          <t>-0.524751772410361</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-49.61</t>
+          <t>-0.496095798371234</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-51.39</t>
+          <t>-0.51392831448078</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-52.06</t>
+          <t>-0.520605641541626</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-52.94</t>
+          <t>-0.529397914059226</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-53.35</t>
+          <t>-0.533527445866847</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-49.93</t>
+          <t>-0.499325759410555</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-47.57</t>
+          <t>-0.475688427997973</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-49.23</t>
+          <t>-0.492302737720241</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>0.206592529308739</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>0.199274034003765</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>35.06</t>
+          <t>0.350762159889287</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>0.420342294244058</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>0.419446604753622</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>0.422686604597048</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>0.267986825561934</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>0.205605649915494</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>0.338256256572875</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>0.426880367359821</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>0.252694098354357</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>0.194091226916802</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>0.129239538082703</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>0.124938327275531</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>0.0534451854475124</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-0.158079920943867</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-0.160940865836413</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-9.64</t>
+          <t>-0.0961675965670307</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-8.82</t>
+          <t>-0.0882998834777408</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-0.0918560694159152</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-11.01</t>
+          <t>-0.110017652504527</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>-0.100577165195848</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-0.0992425682116984</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-0.121254058627797</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-20.66</t>
+          <t>-0.206641131686783</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-17.17</t>
+          <t>-0.171723499862075</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-15.63</t>
+          <t>-0.156230801069244</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-0.0715853505982238</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.0179852411667383</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>0.108188986250278</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-16.36</t>
+          <t>-0.163129332652475</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-0.0461164043611242</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>0.0747878855786086</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>0.11241181540592</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>0.0414467014387003</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.011189913037905</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>0.0240898858324075</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.0552190526031784</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>0.0521910496151046</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.01320754200103</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-0.0158068178622232</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>0.0402641176666005</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>0.153428007551352</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>0.182201900928544</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>0.129387988100841</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>0.10303149833752</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>0.150707634675457</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.280489126551564</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>0.44861126704603</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>52.83</t>
+          <t>0.500555868766896</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>0.469169357801223</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>0.445997582831108</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>0.488319584750837</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>0.406989670051751</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>0.423440555937979</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>38.83</t>
+          <t>0.388448552835148</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>34.91</t>
+          <t>0.349227234621504</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>38.34</t>
+          <t>0.383632007794584</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>50.96</t>
+          <t>0.509411760039127</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>0.587188976766977</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>134.88</t>
+          <t>1.34853235128519</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>122.53</t>
+          <t>1.22510702278274</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>123.87</t>
+          <t>1.23886632891714</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>79.83</t>
+          <t>0.798424311055906</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>0.681480888250162</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>75.54</t>
+          <t>0.75541442246066</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>80.12</t>
+          <t>0.801427633249201</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>72.45</t>
+          <t>0.724708656869212</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>66.82</t>
+          <t>0.667927015736202</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>89.99</t>
+          <t>0.899763740943206</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>0.897584957804003</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>84.78</t>
+          <t>0.848151037708904</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>102.21</t>
+          <t>1.02233087133454</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>0.907993129020367</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>96.04</t>
+          <t>0.960432943308144</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-0.121226452153183</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.00831792917729912</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>0.192676036613049</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>0.129035135447526</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>0.00665090157288373</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-0.0510214139476973</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>0.0345475010525103</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.0296328845371563</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.00273178390225837</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-0.0887273797603841</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-12.38</t>
+          <t>-0.123804400684024</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>-10.63</t>
+          <t>-0.106246629192002</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>0.0392070158445981</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-0.0640514435727402</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>0.12198066648382</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>153.41</t>
+          <t>1.53450951613253</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>146.12</t>
+          <t>1.46146273047302</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>145.06</t>
+          <t>1.45073185349038</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>130.23</t>
+          <t>1.30227115446237</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>123.17</t>
+          <t>1.20739278254817</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>153.22</t>
+          <t>1.53248623724274</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>160.95</t>
+          <t>1.60992712352306</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>168.01</t>
+          <t>1.68043695894077</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>168.85</t>
+          <t>1.688693287867</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>156.76</t>
+          <t>1.5675976677466</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>150.73</t>
+          <t>1.50743579119304</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>135.89</t>
+          <t>1.35921217876853</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>109.27</t>
+          <t>1.09294486308103</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>80.33</t>
+          <t>0.803080422632752</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>97.09</t>
+          <t>0.970915481144917</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>104.37</t>
+          <t>1.043867656014</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>118.02</t>
+          <t>1.18030945557531</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>135.02</t>
+          <t>1.35031024383262</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>112.19</t>
+          <t>1.1218958272117</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>99.29</t>
+          <t>0.952412696050823</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>0.944704748843874</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>77.63</t>
+          <t>0.776623855632386</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>79.97</t>
+          <t>0.800071838044178</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>79.09</t>
+          <t>0.791047270155129</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>0.885026058257324</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>115.85</t>
+          <t>1.15857381066371</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>117.05</t>
+          <t>1.1707155559488</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>124.56</t>
+          <t>1.24582523594593</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>131.18</t>
+          <t>1.31177182478546</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>131.67</t>
+          <t>1.31675550778259</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>29.54</t>
+          <t>0.295623166253744</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>0.17596069392481</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>0.422439075330671</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>31.19</t>
+          <t>0.311889000055085</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>0.133889411471156</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>0.0852247913352564</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-18.87</t>
+          <t>-0.188576719776036</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-10.52</t>
+          <t>-0.105057260178602</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00199895381962811</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>0.0827262498746555</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>0.0370051749651952</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>0.0822072309582282</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.014940201059255</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.00096366991322383</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>0.110390569763568</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-46.63</t>
+          <t>-0.46628071039423</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-42.75</t>
+          <t>-0.427522380649738</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-17.73</t>
+          <t>-0.177273552825727</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-32.66</t>
+          <t>-0.326591517792254</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-35.8</t>
+          <t>-0.367137440241802</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-34.28</t>
+          <t>-0.342816009988695</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-40.96</t>
+          <t>-0.409559297507507</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-47.17</t>
+          <t>-0.471625658795339</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-42.18</t>
+          <t>-0.421821204979165</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-44.64</t>
+          <t>-0.446466160344117</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-43.04</t>
+          <t>-0.430397938911098</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-43.04</t>
+          <t>-0.430412485473912</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-40.65</t>
+          <t>-0.406441453916042</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-43.89</t>
+          <t>-0.438935520200403</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-41.75</t>
+          <t>-0.417507221371406</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>0.0761112354943079</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>0.0367337406944968</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>0.0269242607093318</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.0107696774411832</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>0.0857977200617865</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>0.149049315426889</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>0.43277181206214</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>0.476525337626075</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>69.52</t>
+          <t>0.695258761877194</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>70.19</t>
+          <t>0.701838591708629</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>66.92</t>
+          <t>0.669301431236559</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>73.63</t>
+          <t>0.736488081745364</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>73.38</t>
+          <t>0.734054441261085</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>0.71803762291704</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>95.88</t>
+          <t>0.958860625209306</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-23.05</t>
+          <t>-0.230396911277106</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-24.04</t>
+          <t>-0.24035058765349</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-13.88</t>
+          <t>-0.13876004809884</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-22.94</t>
+          <t>-0.229430307607899</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-22.4</t>
+          <t>-0.23496103699759</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-23.21</t>
+          <t>-0.232000378789658</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-25.34</t>
+          <t>-0.253297614083789</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-24.07</t>
+          <t>-0.240630389116644</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-0.0541795092593045</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-20.65</t>
+          <t>-0.20651272313442</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>-19.2</t>
+          <t>-0.191945000844331</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-0.0574877503089578</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-0.01187547085326</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.00603622623882305</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>0.167074786985604</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>0.441133148850499</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>0.463043218266963</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>54.53</t>
+          <t>0.545313972306213</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>0.33149771846775</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0.00722467691286122</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-0.0639261328650371</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-0.058783418756988</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>0.237274789612572</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>58.02</t>
+          <t>0.580245306595283</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>0.467363338651781</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>0.317876904986773</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>0.367181293317905</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>32.82</t>
+          <t>0.328300448454468</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>0.273606256382209</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>0.404610378670845</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>0.264235710392785</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>0.223193590527002</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>0.278536790536348</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>0.361932299712073</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>0.521299849191003</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>0.375439745014009</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>0.35297128204486</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>27.71</t>
+          <t>0.27713919915023</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>0.150892049051015</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>0.121241527876049</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>0.0556660658268855</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>0.0484446128212426</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-0.0565015381323002</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>-21.15</t>
+          <t>-0.211592205670324</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-0.238499457100154</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>241.73</t>
+          <t>2.41772526306024</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>202.95</t>
+          <t>2.02973634756771</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>220.75</t>
+          <t>2.20782104531548</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>223.16</t>
+          <t>2.23153923709049</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>230.41</t>
+          <t>2.25298913738096</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>215.67</t>
+          <t>2.15686012368716</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>216.88</t>
+          <t>2.16928805073051</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>225.77</t>
+          <t>2.25816608215795</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>192.86</t>
+          <t>1.92861666156706</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>121.46</t>
+          <t>1.2145269487624</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>118.3</t>
+          <t>1.18321946310569</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>104.99</t>
+          <t>1.04991268891748</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>83.25</t>
+          <t>0.832123931467437</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>0.882160948654652</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>58.17</t>
+          <t>0.581739907538254</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-18.4</t>
+          <t>-0.183779510743415</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-15.1</t>
+          <t>-0.150845502150622</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-0.0393890624291736</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-0.0869103157892998</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-0.0810286278138141</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-0.0756532388443947</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-13.47</t>
+          <t>-0.134736648201589</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-11.83</t>
+          <t>-0.118241181004714</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-17.51</t>
+          <t>-0.175116034174735</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-11.76</t>
+          <t>-0.117753572085689</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-7.2</t>
+          <t>-0.0720864809752236</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.0188028869632227</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.0197517612891489</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-23.92</t>
+          <t>-0.239153021420982</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>-22.52</t>
+          <t>-0.225147015902258</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00217186928048929</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.0174976808833219</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>0.141099127894493</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>0.0722633727514164</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>0.0441791107082177</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.0128466189325032</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.0144820625514588</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-0.035814453275714</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-0.0723683565039086</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-11.74</t>
+          <t>-0.117440839998985</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-13.79</t>
+          <t>-0.13780626108191</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-12.27</t>
+          <t>-0.122610906472939</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>-13.15</t>
+          <t>-0.1313235543521</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-0.0354495074572018</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>0.106329408237472</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>0.251812260965147</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>0.143152554580756</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>0.111553968369317</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>0.125229447495022</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-0.038725407652931</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>0.174371382777661</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>0.244436455725351</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>0.468326597741956</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>0.440899726768057</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>0.345010095915784</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>51.24</t>
+          <t>0.512428718347966</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>59.71</t>
+          <t>0.597207028060343</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>61.97</t>
+          <t>0.619884137850683</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-0.0338560415580734</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>0.0880789226463154</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>0.0628773708951975</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.0143209935650876</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>0.133107961220836</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>0.193769109830469</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>0.209372232415401</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>0.171590183252587</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>0.157928681996473</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>0.200673804885606</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>0.213697565906432</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>25.29</t>
+          <t>0.252998275981703</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>0.302408968980592</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>0.363571235403857</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>55.14</t>
+          <t>0.551634262700058</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>59.07</t>
+          <t>0.590746819892097</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>77.92</t>
+          <t>0.779227520303792</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>0.198782497957334</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22.64</t>
+          <t>0.226725739398842</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>0.210987336338287</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>0.144956685871376</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>0.10746739433233</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.0194161505930672</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-0.0633483238175728</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-0.0828199703331701</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-0.112812328353985</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-13.91</t>
+          <t>-0.13906916474522</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>-0.139335730486361</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-12.25</t>
+          <t>-0.122472748885396</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-0.0316058634480764</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0311423332945806</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>0.0514944858033104</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-64.47</t>
+          <t>-0.644676124141116</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-61.9</t>
+          <t>-0.619032822060448</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>-61.92</t>
+          <t>-0.619239195643842</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-62.69</t>
+          <t>-0.626858399761266</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-63.59</t>
+          <t>-0.642648019300794</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-63.22</t>
+          <t>-0.632211339313187</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-61.46</t>
+          <t>-0.614631882024464</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-62.03</t>
+          <t>-0.620331281823378</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>-58.87</t>
+          <t>-0.58872471412055</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-55.98</t>
+          <t>-0.559769514453377</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>-56.4</t>
+          <t>-0.563961197722037</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>-55.78</t>
+          <t>-0.557747453489748</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>-50.44</t>
+          <t>-0.504394046476434</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>-46.74</t>
+          <t>-0.467366199093216</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>-46.69</t>
+          <t>-0.466862888628526</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>-39.18</t>
+          <t>-0.391751499064687</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-36.01</t>
+          <t>-0.360074470715682</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>-35.01</t>
+          <t>-0.350033319132006</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-35.91</t>
+          <t>-0.359074955054163</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-36.42</t>
+          <t>-0.374148245012232</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-37.98</t>
+          <t>-0.37980241275009</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-37.65</t>
+          <t>-0.376423824157218</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-37.67</t>
+          <t>-0.376613447084889</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>-36.87</t>
+          <t>-0.368668861904777</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-36.13</t>
+          <t>-0.361301765716156</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>-36.48</t>
+          <t>-0.364807286903154</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-35.85</t>
+          <t>-0.358521924477599</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>-30.9</t>
+          <t>-0.308962875346853</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>-28.08</t>
+          <t>-0.280840415625458</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>-27.95</t>
+          <t>-0.279554757609855</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
